--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>110904398</v>
       </c>
       <c r="B12" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1872,14 +1872,14 @@
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Flattjärnen (Flattjärnen), Mpd</t>
+          <t>Flattjärnen, Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>562155.1756387679</v>
+        <v>562155</v>
       </c>
       <c r="R12" t="n">
-        <v>6908166.713852912</v>
+        <v>6908167</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1909,19 +1909,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -2064,7 +2054,7 @@
         <v>110904259</v>
       </c>
       <c r="B14" t="n">
-        <v>56398</v>
+        <v>57478</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2103,14 +2093,14 @@
       </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Flattjärnen (Flattjärnen), Mpd</t>
+          <t>Flattjärnen, Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>562123.0518131519</v>
+        <v>562123</v>
       </c>
       <c r="R14" t="n">
-        <v>6908190.314773613</v>
+        <v>6908191</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2140,19 +2130,9 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -2058,7 +2058,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Ovaliderad</t>
+          <t>Behöver inte valideras</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>110904398</v>
       </c>
       <c r="B12" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>110904259</v>
       </c>
       <c r="B14" t="n">
-        <v>57478</v>
+        <v>57481</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -1825,7 +1825,7 @@
         <v>110904398</v>
       </c>
       <c r="B12" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -2054,7 +2054,7 @@
         <v>110904259</v>
       </c>
       <c r="B14" t="n">
-        <v>57481</v>
+        <v>57487</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY21"/>
+  <dimension ref="A1:AY63"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2908,6 +2908,4855 @@
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>131771674</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>562160</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6908094</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>09:18</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>131771638</v>
+      </c>
+      <c r="B23" t="n">
+        <v>91792</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>562345</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6908204</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>11:25</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>131771689</v>
+      </c>
+      <c r="B24" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>562109</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6908176</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>131771685</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>562134</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6908163</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>08:53</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>131771642</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>562535</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6908242</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>131771671</v>
+      </c>
+      <c r="B27" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>562206</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6908099</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>131771686</v>
+      </c>
+      <c r="B28" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>562118</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6908176</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>131771634</v>
+      </c>
+      <c r="B29" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>562398</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6908163</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>131771632</v>
+      </c>
+      <c r="B30" t="n">
+        <v>83107</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>562285</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6908124</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>11:38</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>131771637</v>
+      </c>
+      <c r="B31" t="n">
+        <v>57087</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>562342</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6908229</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flög upp när jag kom för nära.</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>131771681</v>
+      </c>
+      <c r="B32" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>562164</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6908152</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>09:03</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>131771663</v>
+      </c>
+      <c r="B33" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>562291</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6908073</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>131771682</v>
+      </c>
+      <c r="B34" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>562162</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6908151</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>131771683</v>
+      </c>
+      <c r="B35" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>562170</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6908145</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>09:01</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>131771687</v>
+      </c>
+      <c r="B36" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>562105</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6908177</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>131771660</v>
+      </c>
+      <c r="B37" t="n">
+        <v>92289</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>562480</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6908046</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>09:58</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>131771680</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>562180</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6908145</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z38" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB38" t="inlineStr">
+        <is>
+          <t>09:06</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>131771678</v>
+      </c>
+      <c r="B39" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>562188</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6908119</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>131771669</v>
+      </c>
+      <c r="B40" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>562245</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6908143</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>131771690</v>
+      </c>
+      <c r="B41" t="n">
+        <v>83107</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>1312</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Gammelgransskål</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Pseudographis pinicola</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>562126</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6908188</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>08:44</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>131771667</v>
+      </c>
+      <c r="B42" t="n">
+        <v>80366</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>562228</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6908109</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>09:37</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>131771676</v>
+      </c>
+      <c r="B43" t="n">
+        <v>92289</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>1209</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Rynkskinn</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Hermanssonia centrifuga</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(P. Karst.) Zmitr.</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>562171</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6908084</v>
+      </c>
+      <c r="S43" t="n">
+        <v>10</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>09:16</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>131771549</v>
+      </c>
+      <c r="B44" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr"/>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>562117</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6908234</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>08:34</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>131771666</v>
+      </c>
+      <c r="B45" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr"/>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>562222</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6908095</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>09:38</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>131771684</v>
+      </c>
+      <c r="B46" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr"/>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>562126</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6908151</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>08:55</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>131771656</v>
+      </c>
+      <c r="B47" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>562583</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6908052</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>10:09</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>131771639</v>
+      </c>
+      <c r="B48" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>562371</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6908200</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>11:23</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>131771670</v>
+      </c>
+      <c r="B49" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>562225</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6908128</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>09:29</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>131771655</v>
+      </c>
+      <c r="B50" t="n">
+        <v>79261</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>562596</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6908053</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>10:11</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>131771675</v>
+      </c>
+      <c r="B51" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>562171</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6908087</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>131771664</v>
+      </c>
+      <c r="B52" t="n">
+        <v>97148</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>562280</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6908063</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>09:46</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>131771658</v>
+      </c>
+      <c r="B53" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>562522</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6908051</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>131771661</v>
+      </c>
+      <c r="B54" t="n">
+        <v>92128</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>658</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Fomitopsis rosea</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>562478</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6908047</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>09:57</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>131771640</v>
+      </c>
+      <c r="B55" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>562467</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6908213</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>131771673</v>
+      </c>
+      <c r="B56" t="n">
+        <v>97148</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>562187</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6908086</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>09:20</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>131771677</v>
+      </c>
+      <c r="B57" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="L57" t="inlineStr"/>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>562180</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6908114</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>09:11</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>131771635</v>
+      </c>
+      <c r="B58" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="K58" t="inlineStr"/>
+      <c r="L58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>562371</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6908187</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>131771679</v>
+      </c>
+      <c r="B59" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>562184</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6908124</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>09:08</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>131771659</v>
+      </c>
+      <c r="B60" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>562517</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6908038</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>10:01</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>färska och äldre ringhack på tall</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>131771672</v>
+      </c>
+      <c r="B61" t="n">
+        <v>57899</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>562203</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6908095</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>131771668</v>
+      </c>
+      <c r="B62" t="n">
+        <v>92429</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>760</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Doftticka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Haploporus odorus</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>562229</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6908111</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>09:36</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>131771665</v>
+      </c>
+      <c r="B63" t="n">
+        <v>97900</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Flattjärnen, Mpd</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>562283</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6908069</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Ånge</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Medelpad</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Torp</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2026-03-19</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>09:45</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Joel Helker-Nygren</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3364,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771642</v>
+        <v>131771686</v>
       </c>
       <c r="B26" t="n">
-        <v>79261</v>
+        <v>57899</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,34 +3375,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562535</v>
+        <v>562118</v>
       </c>
       <c r="R26" t="n">
-        <v>6908242</v>
+        <v>6908176</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3442,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,7 +3452,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3591,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771686</v>
+        <v>131771642</v>
       </c>
       <c r="B28" t="n">
-        <v>57899</v>
+        <v>79261</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,42 +3615,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562118</v>
+        <v>562535</v>
       </c>
       <c r="R28" t="n">
-        <v>6908176</v>
+        <v>6908242</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,12 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131771663</v>
+        <v>131771682</v>
       </c>
       <c r="B33" t="n">
         <v>57899</v>
@@ -4215,7 +4215,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562291</v>
+        <v>562162</v>
       </c>
       <c r="R33" t="n">
-        <v>6908073</v>
+        <v>6908151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,7 +4302,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131771682</v>
+        <v>131771663</v>
       </c>
       <c r="B34" t="n">
         <v>57899</v>
@@ -4335,7 +4335,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562162</v>
+        <v>562291</v>
       </c>
       <c r="R34" t="n">
-        <v>6908151</v>
+        <v>6908073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4542,53 +4542,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771687</v>
+        <v>131771660</v>
       </c>
       <c r="B36" t="n">
-        <v>57899</v>
+        <v>92289</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562105</v>
+        <v>562480</v>
       </c>
       <c r="R36" t="n">
-        <v>6908177</v>
+        <v>6908046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4620,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4630,12 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4662,45 +4649,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B37" t="n">
-        <v>92289</v>
+        <v>57899</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R37" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4732,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4742,7 +4737,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131771678</v>
+        <v>131771690</v>
       </c>
       <c r="B39" t="n">
-        <v>57899</v>
+        <v>83107</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,42 +4887,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562188</v>
+        <v>562126</v>
       </c>
       <c r="R39" t="n">
-        <v>6908119</v>
+        <v>6908188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4954,7 +4946,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:09</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4964,12 +4956,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:09</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5116,10 +5103,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>131771690</v>
+        <v>131771678</v>
       </c>
       <c r="B41" t="n">
-        <v>83107</v>
+        <v>57899</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5127,34 +5114,42 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr"/>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr"/>
       <c r="P41" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562126</v>
+        <v>562188</v>
       </c>
       <c r="R41" t="n">
-        <v>6908188</v>
+        <v>6908119</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -5186,7 +5181,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:09</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5196,7 +5191,12 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:09</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B42" t="n">
-        <v>80366</v>
+        <v>92289</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R42" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B43" t="n">
-        <v>92289</v>
+        <v>80366</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R43" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5917,7 +5917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131771639</v>
+        <v>131771670</v>
       </c>
       <c r="B48" t="n">
         <v>57899</v>
@@ -5950,7 +5950,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562371</v>
+        <v>562225</v>
       </c>
       <c r="R48" t="n">
-        <v>6908200</v>
+        <v>6908128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6037,7 +6037,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131771670</v>
+        <v>131771639</v>
       </c>
       <c r="B49" t="n">
         <v>57899</v>
@@ -6070,7 +6070,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562225</v>
+        <v>562371</v>
       </c>
       <c r="R49" t="n">
-        <v>6908128</v>
+        <v>6908200</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6157,32 +6157,32 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771655</v>
+        <v>131771664</v>
       </c>
       <c r="B50" t="n">
-        <v>79261</v>
+        <v>97148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6192,10 +6192,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562596</v>
+        <v>562280</v>
       </c>
       <c r="R50" t="n">
-        <v>6908053</v>
+        <v>6908063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6227,7 +6227,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6237,7 +6237,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,10 +6264,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771675</v>
+        <v>131771655</v>
       </c>
       <c r="B51" t="n">
-        <v>57899</v>
+        <v>79261</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,42 +6275,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562171</v>
+        <v>562596</v>
       </c>
       <c r="R51" t="n">
-        <v>6908087</v>
+        <v>6908053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6342,7 +6334,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6352,12 +6344,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6384,45 +6371,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771664</v>
+        <v>131771675</v>
       </c>
       <c r="B52" t="n">
-        <v>97148</v>
+        <v>57899</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562280</v>
+        <v>562171</v>
       </c>
       <c r="R52" t="n">
-        <v>6908063</v>
+        <v>6908087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6454,7 +6449,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6464,7 +6459,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131771661</v>
+        <v>131771640</v>
       </c>
       <c r="B54" t="n">
-        <v>92128</v>
+        <v>57899</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6622,34 +6622,42 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562478</v>
+        <v>562467</v>
       </c>
       <c r="R54" t="n">
-        <v>6908047</v>
+        <v>6908213</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6681,7 +6689,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6691,7 +6699,12 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6718,10 +6731,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771640</v>
+        <v>131771661</v>
       </c>
       <c r="B55" t="n">
-        <v>57899</v>
+        <v>92128</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,42 +6742,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562467</v>
+        <v>562478</v>
       </c>
       <c r="R55" t="n">
-        <v>6908213</v>
+        <v>6908047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,7 +6801,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6806,12 +6811,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7425,53 +7425,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771672</v>
+        <v>131771665</v>
       </c>
       <c r="B61" t="n">
-        <v>57899</v>
+        <v>97900</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562203</v>
+        <v>562283</v>
       </c>
       <c r="R61" t="n">
-        <v>6908095</v>
+        <v>6908069</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7503,7 +7495,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7513,12 +7505,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7545,45 +7532,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B62" t="n">
-        <v>92429</v>
+        <v>57899</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R62" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7615,7 +7610,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7620,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,32 +7652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771665</v>
+        <v>131771668</v>
       </c>
       <c r="B63" t="n">
-        <v>97900</v>
+        <v>92429</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>760</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562283</v>
+        <v>562229</v>
       </c>
       <c r="R63" t="n">
-        <v>6908069</v>
+        <v>6908111</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -2913,7 +2913,7 @@
         <v>131771674</v>
       </c>
       <c r="B22" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,45 +3030,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131771638</v>
+        <v>131771689</v>
       </c>
       <c r="B23" t="n">
-        <v>91792</v>
+        <v>57902</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562345</v>
+        <v>562109</v>
       </c>
       <c r="R23" t="n">
-        <v>6908204</v>
+        <v>6908176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,7 +3118,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,53 +3150,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131771689</v>
+        <v>131771638</v>
       </c>
       <c r="B24" t="n">
-        <v>57899</v>
+        <v>91795</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562109</v>
+        <v>562345</v>
       </c>
       <c r="R24" t="n">
-        <v>6908176</v>
+        <v>6908204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3215,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,12 +3230,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,7 +3260,7 @@
         <v>131771685</v>
       </c>
       <c r="B25" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3364,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771686</v>
+        <v>131771642</v>
       </c>
       <c r="B26" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,42 +3375,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562118</v>
+        <v>562535</v>
       </c>
       <c r="R26" t="n">
-        <v>6908176</v>
+        <v>6908242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3442,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3452,12 +3444,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771671</v>
+        <v>131771686</v>
       </c>
       <c r="B27" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3527,10 +3514,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562206</v>
+        <v>562118</v>
       </c>
       <c r="R27" t="n">
-        <v>6908099</v>
+        <v>6908176</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3562,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3572,7 +3559,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC27" t="inlineStr">
@@ -3604,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B28" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,34 +3602,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R28" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3679,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,10 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131771634</v>
+        <v>131771632</v>
       </c>
       <c r="B29" t="n">
-        <v>57899</v>
+        <v>83110</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,42 +3722,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562398</v>
+        <v>562285</v>
       </c>
       <c r="R29" t="n">
-        <v>6908163</v>
+        <v>6908124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,12 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131771632</v>
+        <v>131771634</v>
       </c>
       <c r="B30" t="n">
-        <v>83107</v>
+        <v>57902</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,34 +3829,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562285</v>
+        <v>562398</v>
       </c>
       <c r="R30" t="n">
-        <v>6908124</v>
+        <v>6908163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3896,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3906,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3941,7 +3941,7 @@
         <v>131771637</v>
       </c>
       <c r="B31" t="n">
-        <v>57087</v>
+        <v>57090</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>131771681</v>
       </c>
       <c r="B32" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>131771682</v>
       </c>
       <c r="B33" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>131771663</v>
       </c>
       <c r="B34" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>131771683</v>
       </c>
       <c r="B35" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4545,7 +4545,7 @@
         <v>131771660</v>
       </c>
       <c r="B36" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4652,7 +4652,7 @@
         <v>131771687</v>
       </c>
       <c r="B37" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4772,7 +4772,7 @@
         <v>131771680</v>
       </c>
       <c r="B38" t="n">
-        <v>79261</v>
+        <v>79264</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4879,7 +4879,7 @@
         <v>131771690</v>
       </c>
       <c r="B39" t="n">
-        <v>83107</v>
+        <v>83110</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>131771669</v>
       </c>
       <c r="B40" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>131771678</v>
       </c>
       <c r="B41" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5226,7 +5226,7 @@
         <v>131771676</v>
       </c>
       <c r="B42" t="n">
-        <v>92289</v>
+        <v>92292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>131771667</v>
       </c>
       <c r="B43" t="n">
-        <v>80366</v>
+        <v>80369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5437,10 +5437,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131771549</v>
+        <v>131771666</v>
       </c>
       <c r="B44" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5470,7 +5470,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562117</v>
+        <v>562222</v>
       </c>
       <c r="R44" t="n">
-        <v>6908234</v>
+        <v>6908095</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5557,10 +5557,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131771666</v>
+        <v>131771549</v>
       </c>
       <c r="B45" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5590,7 +5590,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562222</v>
+        <v>562117</v>
       </c>
       <c r="R45" t="n">
-        <v>6908095</v>
+        <v>6908234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5680,7 +5680,7 @@
         <v>131771684</v>
       </c>
       <c r="B46" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>131771656</v>
       </c>
       <c r="B47" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>131771670</v>
       </c>
       <c r="B48" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>131771639</v>
       </c>
       <c r="B49" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>131771664</v>
       </c>
       <c r="B50" t="n">
-        <v>97148</v>
+        <v>97151</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6264,10 +6264,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771655</v>
+        <v>131771675</v>
       </c>
       <c r="B51" t="n">
-        <v>79261</v>
+        <v>57902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,34 +6275,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562596</v>
+        <v>562171</v>
       </c>
       <c r="R51" t="n">
-        <v>6908053</v>
+        <v>6908087</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6334,7 +6342,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6344,7 +6352,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,10 +6384,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771675</v>
+        <v>131771658</v>
       </c>
       <c r="B52" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6414,10 +6427,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562171</v>
+        <v>562522</v>
       </c>
       <c r="R52" t="n">
-        <v>6908087</v>
+        <v>6908051</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6449,7 +6462,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6459,12 +6472,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,10 +6504,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771658</v>
+        <v>131771655</v>
       </c>
       <c r="B53" t="n">
-        <v>57899</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,42 +6515,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562522</v>
+        <v>562596</v>
       </c>
       <c r="R53" t="n">
-        <v>6908051</v>
+        <v>6908053</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6614,7 +6614,7 @@
         <v>131771640</v>
       </c>
       <c r="B54" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6734,7 +6734,7 @@
         <v>131771661</v>
       </c>
       <c r="B55" t="n">
-        <v>92128</v>
+        <v>92131</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6841,7 +6841,7 @@
         <v>131771673</v>
       </c>
       <c r="B56" t="n">
-        <v>97148</v>
+        <v>97151</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6948,7 +6948,7 @@
         <v>131771677</v>
       </c>
       <c r="B57" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>131771635</v>
       </c>
       <c r="B58" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>131771679</v>
       </c>
       <c r="B59" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>131771659</v>
       </c>
       <c r="B60" t="n">
-        <v>57899</v>
+        <v>57902</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7428,7 +7428,7 @@
         <v>131771665</v>
       </c>
       <c r="B61" t="n">
-        <v>97900</v>
+        <v>97903</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7532,53 +7532,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771672</v>
+        <v>131771668</v>
       </c>
       <c r="B62" t="n">
-        <v>57899</v>
+        <v>92432</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562203</v>
+        <v>562229</v>
       </c>
       <c r="R62" t="n">
-        <v>6908095</v>
+        <v>6908111</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7610,7 +7602,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7620,12 +7612,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,45 +7639,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B63" t="n">
-        <v>92429</v>
+        <v>57902</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R63" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7722,7 +7717,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7732,7 +7727,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3030,53 +3030,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131771689</v>
+        <v>131771638</v>
       </c>
       <c r="B23" t="n">
-        <v>57902</v>
+        <v>91795</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562109</v>
+        <v>562345</v>
       </c>
       <c r="R23" t="n">
-        <v>6908176</v>
+        <v>6908204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,12 +3110,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,45 +3137,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131771638</v>
+        <v>131771689</v>
       </c>
       <c r="B24" t="n">
-        <v>91795</v>
+        <v>57902</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562345</v>
+        <v>562109</v>
       </c>
       <c r="R24" t="n">
-        <v>6908204</v>
+        <v>6908176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,7 +3225,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,34 +3268,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R25" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3327,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3337,7 +3345,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,34 +3388,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R26" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,7 +3465,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771686</v>
+        <v>131771685</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,42 +3508,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562118</v>
+        <v>562134</v>
       </c>
       <c r="R27" t="n">
-        <v>6908176</v>
+        <v>6908163</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,12 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771671</v>
+        <v>131771642</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,42 +3615,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562206</v>
+        <v>562535</v>
       </c>
       <c r="R28" t="n">
-        <v>6908099</v>
+        <v>6908242</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,12 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4542,45 +4542,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B36" t="n">
-        <v>92292</v>
+        <v>57902</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R36" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4620,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4630,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4662,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771687</v>
+        <v>131771680</v>
       </c>
       <c r="B37" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,42 +4673,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562105</v>
+        <v>562180</v>
       </c>
       <c r="R37" t="n">
-        <v>6908177</v>
+        <v>6908145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,12 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4769,32 +4769,32 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131771680</v>
+        <v>131771660</v>
       </c>
       <c r="B38" t="n">
-        <v>79264</v>
+        <v>92292</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4804,10 +4804,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562180</v>
+        <v>562480</v>
       </c>
       <c r="R38" t="n">
-        <v>6908145</v>
+        <v>6908046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4839,7 +4839,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4849,7 +4849,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B42" t="n">
-        <v>92292</v>
+        <v>80369</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R42" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B43" t="n">
-        <v>80369</v>
+        <v>92292</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R43" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6264,10 +6264,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771675</v>
+        <v>131771655</v>
       </c>
       <c r="B51" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,42 +6275,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562171</v>
+        <v>562596</v>
       </c>
       <c r="R51" t="n">
-        <v>6908087</v>
+        <v>6908053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6342,7 +6334,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6352,12 +6344,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6384,7 +6371,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771658</v>
+        <v>131771675</v>
       </c>
       <c r="B52" t="n">
         <v>57902</v>
@@ -6427,10 +6414,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562522</v>
+        <v>562171</v>
       </c>
       <c r="R52" t="n">
-        <v>6908051</v>
+        <v>6908087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6462,7 +6449,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6472,12 +6459,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6504,10 +6491,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771655</v>
+        <v>131771658</v>
       </c>
       <c r="B53" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6515,34 +6502,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562596</v>
+        <v>562522</v>
       </c>
       <c r="R53" t="n">
-        <v>6908053</v>
+        <v>6908051</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6584,7 +6579,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6731,32 +6731,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771661</v>
+        <v>131771673</v>
       </c>
       <c r="B55" t="n">
-        <v>92131</v>
+        <v>97151</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562478</v>
+        <v>562187</v>
       </c>
       <c r="R55" t="n">
-        <v>6908047</v>
+        <v>6908086</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6838,32 +6838,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131771673</v>
+        <v>131771661</v>
       </c>
       <c r="B56" t="n">
-        <v>97151</v>
+        <v>92131</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562187</v>
+        <v>562478</v>
       </c>
       <c r="R56" t="n">
-        <v>6908086</v>
+        <v>6908047</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD56" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771686</v>
+        <v>131771685</v>
       </c>
       <c r="B25" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,42 +3268,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562118</v>
+        <v>562134</v>
       </c>
       <c r="R25" t="n">
-        <v>6908176</v>
+        <v>6908163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,7 +3327,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,12 +3337,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771671</v>
+        <v>131771642</v>
       </c>
       <c r="B26" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,42 +3375,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562206</v>
+        <v>562535</v>
       </c>
       <c r="R26" t="n">
-        <v>6908099</v>
+        <v>6908242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,12 +3444,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B27" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,34 +3482,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R27" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3559,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B28" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,34 +3602,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R28" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3679,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4542,53 +4542,45 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771687</v>
+        <v>131771660</v>
       </c>
       <c r="B36" t="n">
-        <v>57902</v>
+        <v>92292</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562105</v>
+        <v>562480</v>
       </c>
       <c r="R36" t="n">
-        <v>6908177</v>
+        <v>6908046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4620,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4630,12 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4769,45 +4756,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B38" t="n">
-        <v>92292</v>
+        <v>57902</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R38" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4839,7 +4834,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4849,7 +4844,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B42" t="n">
-        <v>80369</v>
+        <v>92292</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R42" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B43" t="n">
-        <v>92292</v>
+        <v>80369</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R43" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6157,45 +6157,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771664</v>
+        <v>131771675</v>
       </c>
       <c r="B50" t="n">
-        <v>97151</v>
+        <v>57902</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562280</v>
+        <v>562171</v>
       </c>
       <c r="R50" t="n">
-        <v>6908063</v>
+        <v>6908087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6227,7 +6235,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6237,7 +6245,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,10 +6277,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771655</v>
+        <v>131771658</v>
       </c>
       <c r="B51" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,34 +6288,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562596</v>
+        <v>562522</v>
       </c>
       <c r="R51" t="n">
-        <v>6908053</v>
+        <v>6908051</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6334,7 +6355,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6344,7 +6365,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,53 +6397,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771675</v>
+        <v>131771664</v>
       </c>
       <c r="B52" t="n">
-        <v>57902</v>
+        <v>97151</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562171</v>
+        <v>562280</v>
       </c>
       <c r="R52" t="n">
-        <v>6908087</v>
+        <v>6908063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6449,7 +6467,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6459,12 +6477,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,10 +6504,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771658</v>
+        <v>131771655</v>
       </c>
       <c r="B53" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,42 +6515,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562522</v>
+        <v>562596</v>
       </c>
       <c r="R53" t="n">
-        <v>6908051</v>
+        <v>6908053</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6731,32 +6731,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771673</v>
+        <v>131771661</v>
       </c>
       <c r="B55" t="n">
-        <v>97151</v>
+        <v>92131</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6766,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562187</v>
+        <v>562478</v>
       </c>
       <c r="R55" t="n">
-        <v>6908086</v>
+        <v>6908047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,7 +6801,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6838,32 +6838,32 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131771661</v>
+        <v>131771673</v>
       </c>
       <c r="B56" t="n">
-        <v>92131</v>
+        <v>97151</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6873,10 +6873,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562478</v>
+        <v>562187</v>
       </c>
       <c r="R56" t="n">
-        <v>6908047</v>
+        <v>6908086</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6908,7 +6908,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7425,32 +7425,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771665</v>
+        <v>131771668</v>
       </c>
       <c r="B61" t="n">
-        <v>97903</v>
+        <v>92432</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>760</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7460,10 +7460,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562283</v>
+        <v>562229</v>
       </c>
       <c r="R61" t="n">
-        <v>6908069</v>
+        <v>6908111</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7495,7 +7495,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7505,7 +7505,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,45 +7532,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B62" t="n">
-        <v>92432</v>
+        <v>57902</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R62" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7602,7 +7610,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7612,7 +7620,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7639,53 +7652,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771672</v>
+        <v>131771665</v>
       </c>
       <c r="B63" t="n">
-        <v>57902</v>
+        <v>97903</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562203</v>
+        <v>562283</v>
       </c>
       <c r="R63" t="n">
-        <v>6908095</v>
+        <v>6908069</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7717,7 +7722,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7727,12 +7732,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -6157,53 +6157,45 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771675</v>
+        <v>131771664</v>
       </c>
       <c r="B50" t="n">
-        <v>57902</v>
+        <v>97151</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562171</v>
+        <v>562280</v>
       </c>
       <c r="R50" t="n">
-        <v>6908087</v>
+        <v>6908063</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6235,7 +6227,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6245,12 +6237,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6277,10 +6264,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771658</v>
+        <v>131771655</v>
       </c>
       <c r="B51" t="n">
-        <v>57902</v>
+        <v>79264</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6288,42 +6275,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562522</v>
+        <v>562596</v>
       </c>
       <c r="R51" t="n">
-        <v>6908051</v>
+        <v>6908053</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6355,7 +6334,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6365,12 +6344,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6397,45 +6371,53 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771664</v>
+        <v>131771675</v>
       </c>
       <c r="B52" t="n">
-        <v>97151</v>
+        <v>57902</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562280</v>
+        <v>562171</v>
       </c>
       <c r="R52" t="n">
-        <v>6908063</v>
+        <v>6908087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6467,7 +6449,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6477,7 +6459,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6504,10 +6491,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771655</v>
+        <v>131771658</v>
       </c>
       <c r="B53" t="n">
-        <v>79264</v>
+        <v>57902</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6515,34 +6502,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562596</v>
+        <v>562522</v>
       </c>
       <c r="R53" t="n">
-        <v>6908053</v>
+        <v>6908051</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6584,7 +6579,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -2913,7 +2913,7 @@
         <v>131771674</v>
       </c>
       <c r="B22" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3030,45 +3030,53 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131771638</v>
+        <v>131771689</v>
       </c>
       <c r="B23" t="n">
-        <v>91795</v>
+        <v>57904</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562345</v>
+        <v>562109</v>
       </c>
       <c r="R23" t="n">
-        <v>6908204</v>
+        <v>6908176</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3100,7 +3108,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3110,7 +3118,12 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3137,53 +3150,45 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131771689</v>
+        <v>131771638</v>
       </c>
       <c r="B24" t="n">
-        <v>57902</v>
+        <v>91801</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562109</v>
+        <v>562345</v>
       </c>
       <c r="R24" t="n">
-        <v>6908176</v>
+        <v>6908204</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3215,7 +3220,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3225,12 +3230,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3260,7 +3260,7 @@
         <v>131771685</v>
       </c>
       <c r="B25" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3367,7 +3367,7 @@
         <v>131771642</v>
       </c>
       <c r="B26" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3474,7 +3474,7 @@
         <v>131771686</v>
       </c>
       <c r="B27" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3594,7 +3594,7 @@
         <v>131771671</v>
       </c>
       <c r="B28" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3714,7 +3714,7 @@
         <v>131771632</v>
       </c>
       <c r="B29" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3821,7 +3821,7 @@
         <v>131771634</v>
       </c>
       <c r="B30" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3941,7 +3941,7 @@
         <v>131771637</v>
       </c>
       <c r="B31" t="n">
-        <v>57090</v>
+        <v>57092</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4065,7 +4065,7 @@
         <v>131771681</v>
       </c>
       <c r="B32" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>131771682</v>
       </c>
       <c r="B33" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4305,7 +4305,7 @@
         <v>131771663</v>
       </c>
       <c r="B34" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4425,7 +4425,7 @@
         <v>131771683</v>
       </c>
       <c r="B35" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4542,45 +4542,53 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B36" t="n">
-        <v>92292</v>
+        <v>57904</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R36" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4620,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4630,12 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,32 +4662,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771680</v>
+        <v>131771660</v>
       </c>
       <c r="B37" t="n">
-        <v>79264</v>
+        <v>92298</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4684,10 +4697,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562180</v>
+        <v>562480</v>
       </c>
       <c r="R37" t="n">
-        <v>6908145</v>
+        <v>6908046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4732,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4742,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,10 +4769,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131771687</v>
+        <v>131771680</v>
       </c>
       <c r="B38" t="n">
-        <v>57902</v>
+        <v>79266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4767,42 +4780,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562105</v>
+        <v>562180</v>
       </c>
       <c r="R38" t="n">
-        <v>6908177</v>
+        <v>6908145</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4834,7 +4839,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4844,12 +4849,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4879,7 +4879,7 @@
         <v>131771690</v>
       </c>
       <c r="B39" t="n">
-        <v>83110</v>
+        <v>83112</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4986,7 +4986,7 @@
         <v>131771669</v>
       </c>
       <c r="B40" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5106,7 +5106,7 @@
         <v>131771678</v>
       </c>
       <c r="B41" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B42" t="n">
-        <v>92292</v>
+        <v>80371</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R42" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B43" t="n">
-        <v>80369</v>
+        <v>92298</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R43" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5440,7 +5440,7 @@
         <v>131771666</v>
       </c>
       <c r="B44" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5560,7 +5560,7 @@
         <v>131771549</v>
       </c>
       <c r="B45" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>131771684</v>
       </c>
       <c r="B46" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5800,7 +5800,7 @@
         <v>131771656</v>
       </c>
       <c r="B47" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5920,7 +5920,7 @@
         <v>131771670</v>
       </c>
       <c r="B48" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -6040,7 +6040,7 @@
         <v>131771639</v>
       </c>
       <c r="B49" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6160,7 +6160,7 @@
         <v>131771664</v>
       </c>
       <c r="B50" t="n">
-        <v>97151</v>
+        <v>97157</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6267,7 +6267,7 @@
         <v>131771655</v>
       </c>
       <c r="B51" t="n">
-        <v>79264</v>
+        <v>79266</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6374,7 +6374,7 @@
         <v>131771675</v>
       </c>
       <c r="B52" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6494,7 +6494,7 @@
         <v>131771658</v>
       </c>
       <c r="B53" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6611,10 +6611,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131771640</v>
+        <v>131771661</v>
       </c>
       <c r="B54" t="n">
-        <v>57902</v>
+        <v>92137</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6622,42 +6622,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562467</v>
+        <v>562478</v>
       </c>
       <c r="R54" t="n">
-        <v>6908213</v>
+        <v>6908047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6689,7 +6681,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6699,12 +6691,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6731,32 +6718,32 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771661</v>
+        <v>131771673</v>
       </c>
       <c r="B55" t="n">
-        <v>92131</v>
+        <v>97157</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6766,10 +6753,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562478</v>
+        <v>562187</v>
       </c>
       <c r="R55" t="n">
-        <v>6908047</v>
+        <v>6908086</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6811,7 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6838,45 +6825,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131771673</v>
+        <v>131771640</v>
       </c>
       <c r="B56" t="n">
-        <v>97151</v>
+        <v>57904</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562187</v>
+        <v>562467</v>
       </c>
       <c r="R56" t="n">
-        <v>6908086</v>
+        <v>6908213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6908,7 +6903,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6918,7 +6913,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6948,7 +6948,7 @@
         <v>131771677</v>
       </c>
       <c r="B57" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7068,7 +7068,7 @@
         <v>131771635</v>
       </c>
       <c r="B58" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7188,7 +7188,7 @@
         <v>131771679</v>
       </c>
       <c r="B59" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7308,7 +7308,7 @@
         <v>131771659</v>
       </c>
       <c r="B60" t="n">
-        <v>57902</v>
+        <v>57904</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7425,45 +7425,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B61" t="n">
-        <v>92432</v>
+        <v>57904</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R61" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7495,7 +7503,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7505,7 +7513,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,53 +7545,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771672</v>
+        <v>131771668</v>
       </c>
       <c r="B62" t="n">
-        <v>57902</v>
+        <v>92438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562203</v>
+        <v>562229</v>
       </c>
       <c r="R62" t="n">
-        <v>6908095</v>
+        <v>6908111</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7610,7 +7615,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7620,12 +7625,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7655,7 +7655,7 @@
         <v>131771665</v>
       </c>
       <c r="B63" t="n">
-        <v>97903</v>
+        <v>97909</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3030,53 +3030,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131771689</v>
+        <v>131771638</v>
       </c>
       <c r="B23" t="n">
-        <v>57904</v>
+        <v>91801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562109</v>
+        <v>562345</v>
       </c>
       <c r="R23" t="n">
-        <v>6908176</v>
+        <v>6908204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,12 +3110,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,45 +3137,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131771638</v>
+        <v>131771689</v>
       </c>
       <c r="B24" t="n">
-        <v>91801</v>
+        <v>57904</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562345</v>
+        <v>562109</v>
       </c>
       <c r="R24" t="n">
-        <v>6908204</v>
+        <v>6908176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,7 +3225,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B25" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,34 +3268,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R25" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3327,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3337,7 +3345,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B26" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,34 +3388,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R26" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,7 +3465,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,10 +3497,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771686</v>
+        <v>131771685</v>
       </c>
       <c r="B27" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,42 +3508,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562118</v>
+        <v>562134</v>
       </c>
       <c r="R27" t="n">
-        <v>6908176</v>
+        <v>6908163</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,12 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771671</v>
+        <v>131771642</v>
       </c>
       <c r="B28" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,42 +3615,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562206</v>
+        <v>562535</v>
       </c>
       <c r="R28" t="n">
-        <v>6908099</v>
+        <v>6908242</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,12 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B42" t="n">
-        <v>80371</v>
+        <v>92298</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R42" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B43" t="n">
-        <v>92298</v>
+        <v>80371</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R43" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -6157,45 +6157,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771664</v>
+        <v>131771675</v>
       </c>
       <c r="B50" t="n">
-        <v>97157</v>
+        <v>57904</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562280</v>
+        <v>562171</v>
       </c>
       <c r="R50" t="n">
-        <v>6908063</v>
+        <v>6908087</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6227,7 +6235,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6237,7 +6245,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,10 +6277,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771655</v>
+        <v>131771658</v>
       </c>
       <c r="B51" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,34 +6288,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562596</v>
+        <v>562522</v>
       </c>
       <c r="R51" t="n">
-        <v>6908053</v>
+        <v>6908051</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6334,7 +6355,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6344,7 +6365,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,53 +6397,45 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771675</v>
+        <v>131771664</v>
       </c>
       <c r="B52" t="n">
-        <v>57904</v>
+        <v>97157</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562171</v>
+        <v>562280</v>
       </c>
       <c r="R52" t="n">
-        <v>6908087</v>
+        <v>6908063</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6449,7 +6467,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6459,12 +6477,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,10 +6504,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771658</v>
+        <v>131771655</v>
       </c>
       <c r="B53" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6502,42 +6515,34 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562522</v>
+        <v>562596</v>
       </c>
       <c r="R53" t="n">
-        <v>6908051</v>
+        <v>6908053</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7425,53 +7425,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771672</v>
+        <v>131771665</v>
       </c>
       <c r="B61" t="n">
-        <v>57904</v>
+        <v>97909</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562203</v>
+        <v>562283</v>
       </c>
       <c r="R61" t="n">
-        <v>6908095</v>
+        <v>6908069</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7503,7 +7495,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7513,12 +7505,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7545,45 +7532,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B62" t="n">
-        <v>92438</v>
+        <v>57904</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R62" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7615,7 +7610,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7620,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,32 +7652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771665</v>
+        <v>131771668</v>
       </c>
       <c r="B63" t="n">
-        <v>97909</v>
+        <v>92438</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>760</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562283</v>
+        <v>562229</v>
       </c>
       <c r="R63" t="n">
-        <v>6908069</v>
+        <v>6908111</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771686</v>
+        <v>131771685</v>
       </c>
       <c r="B25" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,42 +3268,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562118</v>
+        <v>562134</v>
       </c>
       <c r="R25" t="n">
-        <v>6908176</v>
+        <v>6908163</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,7 +3327,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,12 +3337,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771671</v>
+        <v>131771642</v>
       </c>
       <c r="B26" t="n">
-        <v>57904</v>
+        <v>79266</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,42 +3375,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562206</v>
+        <v>562535</v>
       </c>
       <c r="R26" t="n">
-        <v>6908099</v>
+        <v>6908242</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,12 +3444,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B27" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,34 +3482,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R27" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3559,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B28" t="n">
-        <v>79266</v>
+        <v>57904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,34 +3602,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R28" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3679,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -7425,45 +7425,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771665</v>
+        <v>131771672</v>
       </c>
       <c r="B61" t="n">
-        <v>97909</v>
+        <v>57904</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562283</v>
+        <v>562203</v>
       </c>
       <c r="R61" t="n">
-        <v>6908069</v>
+        <v>6908095</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7495,7 +7503,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7505,7 +7513,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,53 +7545,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771672</v>
+        <v>131771668</v>
       </c>
       <c r="B62" t="n">
-        <v>57904</v>
+        <v>92438</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562203</v>
+        <v>562229</v>
       </c>
       <c r="R62" t="n">
-        <v>6908095</v>
+        <v>6908111</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7610,7 +7615,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7620,12 +7625,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,32 +7652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771668</v>
+        <v>131771665</v>
       </c>
       <c r="B63" t="n">
-        <v>92438</v>
+        <v>97909</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7687,10 +7687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562229</v>
+        <v>562283</v>
       </c>
       <c r="R63" t="n">
-        <v>6908111</v>
+        <v>6908069</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7722,7 +7722,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7732,7 +7732,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3030,53 +3030,45 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>131771689</v>
+        <v>131771638</v>
       </c>
       <c r="B23" t="n">
-        <v>57948</v>
+        <v>91855</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562109</v>
+        <v>562345</v>
       </c>
       <c r="R23" t="n">
-        <v>6908176</v>
+        <v>6908204</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3108,7 +3100,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3118,12 +3110,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:25</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3150,45 +3137,53 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>131771638</v>
+        <v>131771689</v>
       </c>
       <c r="B24" t="n">
-        <v>91852</v>
+        <v>57948</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562345</v>
+        <v>562109</v>
       </c>
       <c r="R24" t="n">
-        <v>6908204</v>
+        <v>6908176</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3220,7 +3215,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3230,7 +3225,12 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>11:25</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771685</v>
+        <v>131771671</v>
       </c>
       <c r="B25" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,34 +3268,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562134</v>
+        <v>562206</v>
       </c>
       <c r="R25" t="n">
-        <v>6908163</v>
+        <v>6908099</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3327,7 +3335,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3337,7 +3345,12 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3364,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771642</v>
+        <v>131771685</v>
       </c>
       <c r="B26" t="n">
-        <v>79315</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3399,10 +3412,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562535</v>
+        <v>562134</v>
       </c>
       <c r="R26" t="n">
-        <v>6908242</v>
+        <v>6908163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3434,7 +3447,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3444,7 +3457,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3471,10 +3484,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771686</v>
+        <v>131771642</v>
       </c>
       <c r="B27" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3482,42 +3495,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562118</v>
+        <v>562535</v>
       </c>
       <c r="R27" t="n">
-        <v>6908176</v>
+        <v>6908242</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3549,7 +3554,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3559,12 +3564,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,7 +3591,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771671</v>
+        <v>131771686</v>
       </c>
       <c r="B28" t="n">
         <v>57948</v>
@@ -3634,10 +3634,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562206</v>
+        <v>562118</v>
       </c>
       <c r="R28" t="n">
-        <v>6908099</v>
+        <v>6908176</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AC28" t="inlineStr">
@@ -3831,57 +3831,45 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131771637</v>
+        <v>131771632</v>
       </c>
       <c r="B30" t="n">
-        <v>57136</v>
+        <v>83163</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100138</v>
+        <v>1312</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>förbiflygande</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562342</v>
+        <v>562285</v>
       </c>
       <c r="R30" t="n">
-        <v>6908229</v>
+        <v>6908124</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3913,7 +3901,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:26</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3923,12 +3911,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:26</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Flög upp när jag kom för nära.</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3955,45 +3938,57 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>131771632</v>
+        <v>131771637</v>
       </c>
       <c r="B31" t="n">
-        <v>83161</v>
+        <v>57136</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1312</v>
+        <v>100138</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>förbiflygande</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562285</v>
+        <v>562342</v>
       </c>
       <c r="R31" t="n">
-        <v>6908124</v>
+        <v>6908229</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4025,7 +4020,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:26</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4035,7 +4030,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:26</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Flög upp när jag kom för nära.</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131771682</v>
+        <v>131771663</v>
       </c>
       <c r="B33" t="n">
         <v>57948</v>
@@ -4215,7 +4215,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562162</v>
+        <v>562291</v>
       </c>
       <c r="R33" t="n">
-        <v>6908151</v>
+        <v>6908073</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,7 +4302,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131771663</v>
+        <v>131771682</v>
       </c>
       <c r="B34" t="n">
         <v>57948</v>
@@ -4335,7 +4335,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562291</v>
+        <v>562162</v>
       </c>
       <c r="R34" t="n">
-        <v>6908073</v>
+        <v>6908151</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4542,32 +4542,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771680</v>
+        <v>131771660</v>
       </c>
       <c r="B36" t="n">
-        <v>79315</v>
+        <v>92352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562180</v>
+        <v>562480</v>
       </c>
       <c r="R36" t="n">
-        <v>6908145</v>
+        <v>6908046</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,10 +4649,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771687</v>
+        <v>131771680</v>
       </c>
       <c r="B37" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4660,42 +4660,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562105</v>
+        <v>562180</v>
       </c>
       <c r="R37" t="n">
-        <v>6908177</v>
+        <v>6908145</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4727,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4737,12 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4769,45 +4756,53 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B38" t="n">
-        <v>92349</v>
+        <v>57948</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R38" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4839,7 +4834,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4849,7 +4844,12 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131771690</v>
+        <v>131771669</v>
       </c>
       <c r="B39" t="n">
-        <v>83161</v>
+        <v>57948</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,34 +4887,42 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr"/>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562126</v>
+        <v>562245</v>
       </c>
       <c r="R39" t="n">
-        <v>6908188</v>
+        <v>6908143</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4946,7 +4954,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4956,7 +4964,12 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4983,10 +4996,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131771669</v>
+        <v>131771690</v>
       </c>
       <c r="B40" t="n">
-        <v>57948</v>
+        <v>83163</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4994,42 +5007,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562245</v>
+        <v>562126</v>
       </c>
       <c r="R40" t="n">
-        <v>6908143</v>
+        <v>6908188</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5061,7 +5066,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5071,12 +5076,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5226,7 +5226,7 @@
         <v>131771667</v>
       </c>
       <c r="B42" t="n">
-        <v>80420</v>
+        <v>80422</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5333,7 +5333,7 @@
         <v>131771676</v>
       </c>
       <c r="B43" t="n">
-        <v>92349</v>
+        <v>92352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5437,7 +5437,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131771666</v>
+        <v>131771549</v>
       </c>
       <c r="B44" t="n">
         <v>57948</v>
@@ -5470,7 +5470,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562222</v>
+        <v>562117</v>
       </c>
       <c r="R44" t="n">
-        <v>6908095</v>
+        <v>6908234</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5557,7 +5557,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131771549</v>
+        <v>131771666</v>
       </c>
       <c r="B45" t="n">
         <v>57948</v>
@@ -5590,7 +5590,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562117</v>
+        <v>562222</v>
       </c>
       <c r="R45" t="n">
-        <v>6908234</v>
+        <v>6908095</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5917,7 +5917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131771670</v>
+        <v>131771639</v>
       </c>
       <c r="B48" t="n">
         <v>57948</v>
@@ -5950,7 +5950,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562225</v>
+        <v>562371</v>
       </c>
       <c r="R48" t="n">
-        <v>6908128</v>
+        <v>6908200</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6037,7 +6037,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131771639</v>
+        <v>131771670</v>
       </c>
       <c r="B49" t="n">
         <v>57948</v>
@@ -6070,7 +6070,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562371</v>
+        <v>562225</v>
       </c>
       <c r="R49" t="n">
-        <v>6908200</v>
+        <v>6908128</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6157,45 +6157,53 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771664</v>
+        <v>131771658</v>
       </c>
       <c r="B50" t="n">
-        <v>97208</v>
+        <v>57948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562280</v>
+        <v>562522</v>
       </c>
       <c r="R50" t="n">
-        <v>6908063</v>
+        <v>6908051</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6227,7 +6235,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6237,7 +6245,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6264,10 +6277,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771655</v>
+        <v>131771675</v>
       </c>
       <c r="B51" t="n">
-        <v>79315</v>
+        <v>57948</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6275,34 +6288,42 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
+      <c r="K51" t="inlineStr"/>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562596</v>
+        <v>562171</v>
       </c>
       <c r="R51" t="n">
-        <v>6908053</v>
+        <v>6908087</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6334,7 +6355,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6344,7 +6365,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6371,10 +6397,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771675</v>
+        <v>131771655</v>
       </c>
       <c r="B52" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6382,42 +6408,34 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562171</v>
+        <v>562596</v>
       </c>
       <c r="R52" t="n">
-        <v>6908087</v>
+        <v>6908053</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6449,7 +6467,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6459,12 +6477,7 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6491,53 +6504,45 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771658</v>
+        <v>131771664</v>
       </c>
       <c r="B53" t="n">
-        <v>57948</v>
+        <v>97211</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562522</v>
+        <v>562280</v>
       </c>
       <c r="R53" t="n">
-        <v>6908051</v>
+        <v>6908063</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6569,7 +6574,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6579,12 +6584,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6611,10 +6611,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131771640</v>
+        <v>131771661</v>
       </c>
       <c r="B54" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6622,42 +6622,34 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562467</v>
+        <v>562478</v>
       </c>
       <c r="R54" t="n">
-        <v>6908213</v>
+        <v>6908047</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6689,7 +6681,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6699,12 +6691,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6731,10 +6718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771661</v>
+        <v>131771640</v>
       </c>
       <c r="B55" t="n">
-        <v>92188</v>
+        <v>57948</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6742,34 +6729,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="K55" t="inlineStr"/>
+      <c r="L55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562478</v>
+        <v>562467</v>
       </c>
       <c r="R55" t="n">
-        <v>6908047</v>
+        <v>6908213</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6801,7 +6796,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6811,7 +6806,12 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6841,7 +6841,7 @@
         <v>131771673</v>
       </c>
       <c r="B56" t="n">
-        <v>97208</v>
+        <v>97211</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -7425,53 +7425,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771672</v>
+        <v>131771668</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>92492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562203</v>
+        <v>562229</v>
       </c>
       <c r="R61" t="n">
-        <v>6908095</v>
+        <v>6908111</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7503,7 +7495,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7513,12 +7505,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7545,32 +7532,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771668</v>
+        <v>131771665</v>
       </c>
       <c r="B62" t="n">
-        <v>92489</v>
+        <v>97963</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>760</v>
+        <v>221945</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7580,10 +7567,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562229</v>
+        <v>562283</v>
       </c>
       <c r="R62" t="n">
-        <v>6908111</v>
+        <v>6908069</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7615,7 +7602,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7612,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7652,45 +7639,53 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771665</v>
+        <v>131771672</v>
       </c>
       <c r="B63" t="n">
-        <v>97960</v>
+        <v>57948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>221945</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562283</v>
+        <v>562203</v>
       </c>
       <c r="R63" t="n">
-        <v>6908069</v>
+        <v>6908095</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7722,7 +7717,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7732,7 +7727,12 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -4542,32 +4542,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>131771660</v>
+        <v>131771680</v>
       </c>
       <c r="B36" t="n">
-        <v>92352</v>
+        <v>79317</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1209</v>
+        <v>6425</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4577,10 +4577,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562480</v>
+        <v>562180</v>
       </c>
       <c r="R36" t="n">
-        <v>6908046</v>
+        <v>6908145</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4612,7 +4612,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4622,7 +4622,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>09:06</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4649,32 +4649,32 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771680</v>
+        <v>131771660</v>
       </c>
       <c r="B37" t="n">
-        <v>79317</v>
+        <v>92352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>1209</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4684,10 +4684,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562180</v>
+        <v>562480</v>
       </c>
       <c r="R37" t="n">
-        <v>6908145</v>
+        <v>6908046</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4719,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4729,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:06</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -7425,45 +7425,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B61" t="n">
-        <v>92492</v>
+        <v>57948</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R61" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7495,7 +7503,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7505,7 +7513,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7532,32 +7545,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771665</v>
+        <v>131771668</v>
       </c>
       <c r="B62" t="n">
-        <v>97963</v>
+        <v>92492</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>221945</v>
+        <v>760</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7567,10 +7580,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562283</v>
+        <v>562229</v>
       </c>
       <c r="R62" t="n">
-        <v>6908069</v>
+        <v>6908111</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7602,7 +7615,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7612,7 +7625,7 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:45</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7639,53 +7652,45 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>131771672</v>
+        <v>131771665</v>
       </c>
       <c r="B63" t="n">
-        <v>57948</v>
+        <v>97963</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>221945</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562203</v>
+        <v>562283</v>
       </c>
       <c r="R63" t="n">
-        <v>6908095</v>
+        <v>6908069</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7717,7 +7722,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7727,12 +7732,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:45</t>
         </is>
       </c>
       <c r="AD63" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3377,10 +3377,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B26" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,34 +3388,42 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R26" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3447,7 +3455,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3457,7 +3465,12 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3484,7 +3497,7 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771642</v>
+        <v>131771685</v>
       </c>
       <c r="B27" t="n">
         <v>79317</v>
@@ -3519,10 +3532,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562535</v>
+        <v>562134</v>
       </c>
       <c r="R27" t="n">
-        <v>6908242</v>
+        <v>6908163</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3554,7 +3567,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3564,7 +3577,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3591,10 +3604,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771686</v>
+        <v>131771642</v>
       </c>
       <c r="B28" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3602,42 +3615,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562118</v>
+        <v>562535</v>
       </c>
       <c r="R28" t="n">
-        <v>6908176</v>
+        <v>6908242</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3669,7 +3674,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3679,12 +3684,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4876,10 +4876,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>131771669</v>
+        <v>131771690</v>
       </c>
       <c r="B39" t="n">
-        <v>57948</v>
+        <v>83163</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4887,42 +4887,34 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562245</v>
+        <v>562126</v>
       </c>
       <c r="R39" t="n">
-        <v>6908143</v>
+        <v>6908188</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4954,7 +4946,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>09:31</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4964,12 +4956,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>09:31</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>08:44</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4996,10 +4983,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>131771690</v>
+        <v>131771669</v>
       </c>
       <c r="B40" t="n">
-        <v>83163</v>
+        <v>57948</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5007,34 +4994,42 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr"/>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562126</v>
+        <v>562245</v>
       </c>
       <c r="R40" t="n">
-        <v>6908188</v>
+        <v>6908143</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5066,7 +5061,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:31</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5076,7 +5071,12 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>08:44</t>
+          <t>09:31</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -6157,10 +6157,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>131771658</v>
+        <v>131771655</v>
       </c>
       <c r="B50" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6168,42 +6168,34 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr"/>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562522</v>
+        <v>562596</v>
       </c>
       <c r="R50" t="n">
-        <v>6908051</v>
+        <v>6908053</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6235,7 +6227,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>10:03</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6245,12 +6237,7 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>10:03</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6277,53 +6264,45 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>131771675</v>
+        <v>131771664</v>
       </c>
       <c r="B51" t="n">
-        <v>57948</v>
+        <v>97211</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>2869</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562171</v>
+        <v>562280</v>
       </c>
       <c r="R51" t="n">
-        <v>6908087</v>
+        <v>6908063</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6355,7 +6334,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>09:17</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6365,12 +6344,7 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>09:17</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>färska ringhack på gran</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6397,10 +6371,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>131771655</v>
+        <v>131771675</v>
       </c>
       <c r="B52" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6408,34 +6382,42 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562596</v>
+        <v>562171</v>
       </c>
       <c r="R52" t="n">
-        <v>6908053</v>
+        <v>6908087</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6467,7 +6449,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6477,7 +6459,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6504,45 +6491,53 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>131771664</v>
+        <v>131771658</v>
       </c>
       <c r="B53" t="n">
-        <v>97211</v>
+        <v>57948</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562280</v>
+        <v>562522</v>
       </c>
       <c r="R53" t="n">
-        <v>6908063</v>
+        <v>6908051</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6574,7 +6569,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:03</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6584,7 +6579,12 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>10:03</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD53" t="b">

--- a/artfynd/A 38605-2024 artfynd.xlsx
+++ b/artfynd/A 38605-2024 artfynd.xlsx
@@ -3257,10 +3257,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>131771671</v>
+        <v>131771642</v>
       </c>
       <c r="B25" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3268,42 +3268,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562206</v>
+        <v>562535</v>
       </c>
       <c r="R25" t="n">
-        <v>6908099</v>
+        <v>6908242</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3335,7 +3327,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>09:23</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3345,12 +3337,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>09:23</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3377,10 +3364,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>131771686</v>
+        <v>131771685</v>
       </c>
       <c r="B26" t="n">
-        <v>57948</v>
+        <v>79317</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3388,42 +3375,34 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562118</v>
+        <v>562134</v>
       </c>
       <c r="R26" t="n">
-        <v>6908176</v>
+        <v>6908163</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3455,7 +3434,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>08:50</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3465,12 +3444,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>08:50</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>08:53</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3497,10 +3471,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>131771685</v>
+        <v>131771686</v>
       </c>
       <c r="B27" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3508,34 +3482,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562134</v>
+        <v>562118</v>
       </c>
       <c r="R27" t="n">
-        <v>6908163</v>
+        <v>6908176</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3567,7 +3549,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3577,7 +3559,12 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>08:53</t>
+          <t>08:50</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3604,10 +3591,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>131771642</v>
+        <v>131771671</v>
       </c>
       <c r="B28" t="n">
-        <v>79317</v>
+        <v>57948</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3615,34 +3602,42 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562535</v>
+        <v>562206</v>
       </c>
       <c r="R28" t="n">
-        <v>6908242</v>
+        <v>6908099</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3674,7 +3669,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3684,7 +3679,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>11:14</t>
+          <t>09:23</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3711,10 +3711,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>131771634</v>
+        <v>131771632</v>
       </c>
       <c r="B29" t="n">
-        <v>57948</v>
+        <v>83163</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3722,42 +3722,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562398</v>
+        <v>562285</v>
       </c>
       <c r="R29" t="n">
-        <v>6908163</v>
+        <v>6908124</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3789,7 +3781,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3799,12 +3791,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>11:31</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3831,10 +3818,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>131771632</v>
+        <v>131771634</v>
       </c>
       <c r="B30" t="n">
-        <v>83163</v>
+        <v>57948</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3842,34 +3829,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562285</v>
+        <v>562398</v>
       </c>
       <c r="R30" t="n">
-        <v>6908124</v>
+        <v>6908163</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3901,7 +3896,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3911,7 +3906,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>11:31</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4182,7 +4182,7 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>131771663</v>
+        <v>131771682</v>
       </c>
       <c r="B33" t="n">
         <v>57948</v>
@@ -4215,7 +4215,7 @@
       <c r="L33" t="inlineStr"/>
       <c r="M33" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N33" t="inlineStr"/>
@@ -4225,10 +4225,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562291</v>
+        <v>562162</v>
       </c>
       <c r="R33" t="n">
-        <v>6908073</v>
+        <v>6908151</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4260,7 +4260,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4270,12 +4270,12 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:02</t>
         </is>
       </c>
       <c r="AC33" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4302,7 +4302,7 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>131771682</v>
+        <v>131771663</v>
       </c>
       <c r="B34" t="n">
         <v>57948</v>
@@ -4335,7 +4335,7 @@
       <c r="L34" t="inlineStr"/>
       <c r="M34" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N34" t="inlineStr"/>
@@ -4345,10 +4345,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562162</v>
+        <v>562291</v>
       </c>
       <c r="R34" t="n">
-        <v>6908151</v>
+        <v>6908073</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4380,7 +4380,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4390,12 +4390,12 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>09:02</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AC34" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4649,45 +4649,53 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>131771660</v>
+        <v>131771687</v>
       </c>
       <c r="B37" t="n">
-        <v>92352</v>
+        <v>57948</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1209</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562480</v>
+        <v>562105</v>
       </c>
       <c r="R37" t="n">
-        <v>6908046</v>
+        <v>6908177</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4719,7 +4727,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4729,7 +4737,12 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>09:58</t>
+          <t>08:47</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4756,53 +4769,45 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>131771687</v>
+        <v>131771660</v>
       </c>
       <c r="B38" t="n">
-        <v>57948</v>
+        <v>92352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>1209</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562105</v>
+        <v>562480</v>
       </c>
       <c r="R38" t="n">
-        <v>6908177</v>
+        <v>6908046</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4834,7 +4839,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>08:47</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4844,12 +4849,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:58</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5223,32 +5223,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>131771667</v>
+        <v>131771676</v>
       </c>
       <c r="B42" t="n">
-        <v>80422</v>
+        <v>92352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>1209</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -5258,10 +5258,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562228</v>
+        <v>562171</v>
       </c>
       <c r="R42" t="n">
-        <v>6908109</v>
+        <v>6908084</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5293,7 +5293,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5303,7 +5303,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>09:16</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5330,32 +5330,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>131771676</v>
+        <v>131771667</v>
       </c>
       <c r="B43" t="n">
-        <v>92352</v>
+        <v>80422</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hermanssonia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(P. Karst.) Zmitr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5365,10 +5365,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562171</v>
+        <v>562228</v>
       </c>
       <c r="R43" t="n">
-        <v>6908084</v>
+        <v>6908109</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>09:16</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5437,7 +5437,7 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>131771549</v>
+        <v>131771666</v>
       </c>
       <c r="B44" t="n">
         <v>57948</v>
@@ -5470,7 +5470,7 @@
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N44" t="inlineStr"/>
@@ -5480,10 +5480,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562117</v>
+        <v>562222</v>
       </c>
       <c r="R44" t="n">
-        <v>6908234</v>
+        <v>6908095</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5525,12 +5525,12 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>08:34</t>
+          <t>09:38</t>
         </is>
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>färska ringhack på tall</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5557,7 +5557,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>131771666</v>
+        <v>131771549</v>
       </c>
       <c r="B45" t="n">
         <v>57948</v>
@@ -5590,7 +5590,7 @@
       <c r="L45" t="inlineStr"/>
       <c r="M45" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N45" t="inlineStr"/>
@@ -5600,10 +5600,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562222</v>
+        <v>562117</v>
       </c>
       <c r="R45" t="n">
-        <v>6908095</v>
+        <v>6908234</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5635,7 +5635,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5645,12 +5645,12 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:38</t>
+          <t>08:34</t>
         </is>
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5917,7 +5917,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>131771639</v>
+        <v>131771670</v>
       </c>
       <c r="B48" t="n">
         <v>57948</v>
@@ -5950,7 +5950,7 @@
       <c r="L48" t="inlineStr"/>
       <c r="M48" t="inlineStr">
         <is>
-          <t>äldre spår</t>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N48" t="inlineStr"/>
@@ -5960,10 +5960,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562371</v>
+        <v>562225</v>
       </c>
       <c r="R48" t="n">
-        <v>6908200</v>
+        <v>6908128</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5995,7 +5995,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -6005,12 +6005,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:23</t>
+          <t>09:29</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>äldre ringhack på gran</t>
+          <t>färska ringhack på gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6037,7 +6037,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>131771670</v>
+        <v>131771639</v>
       </c>
       <c r="B49" t="n">
         <v>57948</v>
@@ -6070,7 +6070,7 @@
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N49" t="inlineStr"/>
@@ -6080,10 +6080,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562225</v>
+        <v>562371</v>
       </c>
       <c r="R49" t="n">
-        <v>6908128</v>
+        <v>6908200</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6125,12 +6125,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>09:29</t>
+          <t>11:23</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>färska ringhack på gran</t>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6611,32 +6611,32 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>131771661</v>
+        <v>131771673</v>
       </c>
       <c r="B54" t="n">
-        <v>92191</v>
+        <v>97211</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Fomitopsis rosea</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6646,10 +6646,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562478</v>
+        <v>562187</v>
       </c>
       <c r="R54" t="n">
-        <v>6908047</v>
+        <v>6908086</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6681,7 +6681,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6718,10 +6718,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131771640</v>
+        <v>131771661</v>
       </c>
       <c r="B55" t="n">
-        <v>57948</v>
+        <v>92191</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6729,42 +6729,34 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
-      <c r="K55" t="inlineStr"/>
-      <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562467</v>
+        <v>562478</v>
       </c>
       <c r="R55" t="n">
-        <v>6908213</v>
+        <v>6908047</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6796,7 +6788,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:18</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6806,12 +6798,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>färska ringhack på tall</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6838,45 +6825,53 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>131771673</v>
+        <v>131771640</v>
       </c>
       <c r="B56" t="n">
-        <v>97211</v>
+        <v>57948</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>2869</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="L56" t="inlineStr"/>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562187</v>
+        <v>562467</v>
       </c>
       <c r="R56" t="n">
-        <v>6908086</v>
+        <v>6908213</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6908,7 +6903,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:18</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6918,7 +6913,12 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>11:18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>färska ringhack på tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7425,53 +7425,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>131771672</v>
+        <v>131771668</v>
       </c>
       <c r="B61" t="n">
-        <v>57948</v>
+        <v>92492</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>760</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562203</v>
+        <v>562229</v>
       </c>
       <c r="R61" t="n">
-        <v>6908095</v>
+        <v>6908111</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7503,7 +7495,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:22</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7513,12 +7505,7 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:22</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>äldre ringhack på gran</t>
+          <t>09:36</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7545,45 +7532,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>131771668</v>
+        <v>131771672</v>
       </c>
       <c r="B62" t="n">
-        <v>92492</v>
+        <v>57948</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>760</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Flattjärnen, Mpd</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562229</v>
+        <v>562203</v>
       </c>
       <c r="R62" t="n">
-        <v>6908111</v>
+        <v>6908095</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7615,7 +7610,7 @@
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
@@ -7625,7 +7620,12 @@
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>09:36</t>
+          <t>09:22</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>äldre ringhack på gran</t>
         </is>
       </c>
       <c r="AD62" t="b">
